--- a/AAII_Financials/Quarterly/MCK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>MCK</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>105380000</v>
+      </c>
+      <c r="E8" s="3">
         <v>96295000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>106158000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>103150000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>97827000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>90823000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>95294000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>93651000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>79283000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>76355000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>80898000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>77215000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>74483000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>68910000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>70490000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>70157000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>67154000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>66102000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>68614000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>66576000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>62674000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>59142000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>62599000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>60808000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>55679000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>58535000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>59172000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>57616000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>55728000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>52429000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>56208000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>53075000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>52607000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>51628000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>53617000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>52061000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>51051000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>48713000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>50130000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>49957000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>101695000</v>
+      </c>
+      <c r="E9" s="3">
         <v>92251000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>102488000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>99608000</v>
       </c>
-      <c r="G9" s="3">
-        <v>94556000</v>
-      </c>
       <c r="H9" s="3">
+        <v>94548000</v>
+      </c>
+      <c r="I9" s="3">
         <v>87449000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>92041000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>90403000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>76221000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>72794000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>77769000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>74146000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>71461000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>65973000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>67316000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>67062000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>64131000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>62784000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>65186000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>63224000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>59486000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>55845000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>59448000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>57808000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>52979000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>55199000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>56139000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>54749000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>52941000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>49228000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>53238000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>50271000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>49828000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>48553000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>50902000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>49227000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>48491000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>45917000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>47318000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>47201000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3685000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4044000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3670000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3542000</v>
       </c>
-      <c r="G10" s="3">
-        <v>3271000</v>
-      </c>
       <c r="H10" s="3">
+        <v>3279000</v>
+      </c>
+      <c r="I10" s="3">
         <v>3374000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3253000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3248000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3062000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3561000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3129000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3069000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3022000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2937000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3174000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3095000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3023000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3318000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3428000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3352000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3188000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3297000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3151000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3000000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2700000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3336000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3033000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2867000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2787000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3201000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2970000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2804000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2779000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3075000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2715000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2834000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2560000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2796000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>2812000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>2756000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,16 +1248,17 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>267000</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1252,11 +1266,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>226000</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1264,11 +1278,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>179000</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -1276,11 +1290,11 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3">
         <v>190000</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>8</v>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,175 +1496,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-29000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>21000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10000</v>
       </c>
-      <c r="G14" s="3">
-        <v>22000</v>
-      </c>
       <c r="H14" s="3">
+        <v>236000</v>
+      </c>
+      <c r="I14" s="3">
         <v>-219000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-21000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-78000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>204000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>509000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>26000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>24000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-365000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>8000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>35000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>101000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>84000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>803000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>423000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>63000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>8222000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>129000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-75000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-742000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>479000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>327000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>67000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1576000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>183000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>144000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>718000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>1884000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-91000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>591000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>-11000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>-3945000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>75000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>290000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>195000</v>
+      </c>
+      <c r="E15" s="3">
         <v>63000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>188000</v>
       </c>
       <c r="F15" s="3">
         <v>188000</v>
       </c>
       <c r="G15" s="3">
+        <v>188000</v>
+      </c>
+      <c r="H15" s="3">
         <v>157000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>46000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>153000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>163000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>169000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>58000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>159000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>157000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>159000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>60000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>103959000</v>
+      </c>
+      <c r="E17" s="3">
         <v>94168000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>104518000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>101733000</v>
       </c>
-      <c r="G17" s="3">
-        <v>96769000</v>
-      </c>
       <c r="H17" s="3">
+        <v>96555000</v>
+      </c>
+      <c r="I17" s="3">
         <v>89581000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>94069000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>93109000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>78222000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>74959000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>79747000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>76238000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>73359000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>67937000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>69249000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>69033000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>66118000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>65469000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>68316000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>66228000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>62106000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>58132000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>69961000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>60174000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>55001000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>56942000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>58829000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>57256000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>55121000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>53025000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>55550000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>52412000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>52556000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>52694000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>52783000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>51822000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>50418000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>43989000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>49302000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>49377000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1421000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2127000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1640000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1417000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1058000</v>
-      </c>
       <c r="H18" s="3">
+        <v>1272000</v>
+      </c>
+      <c r="I18" s="3">
         <v>1242000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1225000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>542000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1061000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1396000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1151000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>977000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1124000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>973000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1241000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1124000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1036000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>633000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>298000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>348000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>568000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1010000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-7362000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>634000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>678000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1593000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>343000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>360000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>607000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-596000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>658000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>663000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>51000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-1066000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>834000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>239000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>633000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>4724000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>828000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>580000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="E20" s="3">
         <v>149000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-74000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-62000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-64000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>74000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-69000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-49000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-20000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>60000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-34000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-26000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-38000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>434000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>276000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>175000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>15000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>57000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>20000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>139000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>43000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>71000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>54000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>71000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>27000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-327000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>15000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1266000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>68000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>33000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>59000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-10000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>16000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>51000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-70000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>8000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-107000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>27000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>26000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1682000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2041000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1902000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1667000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1279000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1493000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1214000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1447000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>754000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1250000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1394000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1344000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1160000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1321000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>599000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1665000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1450000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1199000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>852000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>503000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>682000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>829000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1302000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-7081000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>927000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>922000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1497000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>586000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-672000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>904000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-328000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>956000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>893000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>302000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-761000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>998000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>483000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>753000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>4998000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1058000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>820000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E22" s="3">
         <v>61000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>63000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>74000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>49000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>45000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>67000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>78000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>75000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>80000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>64000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>61000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>47000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>79000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>69000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>55000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>45000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>43000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>41000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>45000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>49000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>52000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>55000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>50000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>60000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>65000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>64000</v>
       </c>
       <c r="AD22" s="3">
         <v>64000</v>
       </c>
       <c r="AE22" s="3">
+        <v>64000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>56000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>70000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>67000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>66000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>61000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>79000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>67000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>69000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>68000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>77000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>74000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>78000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1308000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2125000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1630000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1395000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1051000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1515000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1226000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>534000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1084000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1170000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>612000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>916000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1091000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>932000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1448000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1244000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1006000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>647000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>277000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>442000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>562000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1029000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-7363000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>655000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>645000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1201000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>294000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-970000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>619000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-633000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>650000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>587000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1094000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>697000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>178000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>458000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>4674000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>780000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>525000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>276000</v>
+      </c>
+      <c r="E24" s="3">
         <v>270000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>380000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>232000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>220000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>209000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>298000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>247000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>124000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>340000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-18000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>213000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>94000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>106000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>329000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>271000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>199000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>240000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>238000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>132000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>26000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>316000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1189000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>28000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>150000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>129000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>47000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-294000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>136000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>186000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>96000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>53000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>107000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>34000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>563000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>122000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>95000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1044000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>131000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>200000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1032000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1855000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1250000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1163000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>831000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1306000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>928000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>287000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>960000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>830000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>630000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>703000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>997000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>826000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1119000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>973000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>807000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>407000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>39000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>310000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>536000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>713000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6174000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>627000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>495000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1072000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>247000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-676000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>483000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-819000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>554000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>534000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-101000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-1128000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>134000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>56000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>363000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>3630000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>649000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>325000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>614000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1682000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1186000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1110000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>784000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1260000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>879000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>241000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>915000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>791000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>589000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>664000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>958000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>787000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1078000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>932000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>766000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>370000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>267000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>489000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>666000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6226000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>577000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>445000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1015000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>191000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-729000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>429000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-871000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>497000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>480000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-159000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-1189000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>76000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>307000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>3595000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>636000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>308000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3195,29 +3256,29 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>1000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-6000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>2000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-2000</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-3000</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
@@ -3225,55 +3286,58 @@
         <v>0</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>6000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>75000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-28000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>19000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>43000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>827000</v>
       </c>
-      <c r="AL29" s="3">
-        <v>0</v>
-      </c>
       <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
         <v>2000</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-7000</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-149000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>74000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>62000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>64000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-74000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>69000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>49000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>20000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-60000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>34000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>26000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>38000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-434000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-276000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-175000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-15000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-57000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-20000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-139000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-43000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-71000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-54000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-71000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-27000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>327000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1266000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-68000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-33000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-59000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>10000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-51000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>70000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-8000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>107000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-27000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>614000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1682000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1186000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1110000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>784000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1260000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>879000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>241000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>915000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>791000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>589000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>664000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>958000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>787000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1079000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>926000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>768000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>368000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>267000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>486000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>666000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6226000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>577000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>444000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1021000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>186000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-730000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>423000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-796000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>469000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>499000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-138000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-1146000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>903000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>309000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>3588000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>633000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>614000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1682000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1186000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1110000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>784000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1260000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>879000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>241000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>915000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>791000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>589000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>664000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>958000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>787000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1079000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>926000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>768000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>368000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>267000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>486000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>666000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6226000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>577000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>444000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1021000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>186000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-730000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>423000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-796000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>469000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>499000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-138000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-1146000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>903000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>309000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>3588000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>633000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5164000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3975000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2959000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4004000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2418000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5691000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1131000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2509000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2302000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4583000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1982000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2524000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2636000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4678000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2774000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2916000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2233000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3532000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2754000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2151000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2423000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6278000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3577000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3091000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2613000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4015000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2065000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1356000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1947000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2981000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1849000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2118000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2199000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2672000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2619000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2563000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2339000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2783000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2434000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>5464000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,558 +4553,573 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>30316000</v>
+      </c>
+      <c r="E43" s="3">
         <v>27985000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>28213000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>28286000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>28158000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>25643000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>25831000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>25270000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23743000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>21622000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>23066000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>22494000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>21860000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>19410000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>20537000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>20109000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>19900000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>18583000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>18355000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>20140000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>20198000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>19181000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>18877000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>19285000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>17768000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>19950000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>18831000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>18984000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>19287000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>18246000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>18932000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>19213000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>19093000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>17711000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>20015000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>19627000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>19132000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>18215000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>18198000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>18308000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>26259000</v>
+      </c>
+      <c r="E44" s="3">
         <v>24207000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>27067000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>26134000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>25065000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>23001000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>23837000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>24176000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>25571000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>21139000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>22020000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>21945000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>20510000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>19691000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>20657000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>19876000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>19505000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>18702000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>19024000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>19342000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>20016000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>19246000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>19211000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>18435000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>16607000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>16734000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>17020000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>16356000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>16604000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>16709000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>16951000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>16671000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>16364000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>16310000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>17103000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>16885000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>15498000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>15278000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>16121000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>15273000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E45" s="3">
         <v>76000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>190000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>202000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>113000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>55000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>26000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>706000</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13000</v>
       </c>
-      <c r="M45" s="3" t="s">
+      <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6000</v>
       </c>
-      <c r="O45" s="3" t="s">
+      <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>689000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3547000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3745000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5414000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6365000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3947000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>713000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>677000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>703000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1534000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1694000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1523000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1474000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>657000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>590000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>529000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>587000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>542000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>558000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>443000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>458000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>719000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>728000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>672000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>2515000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>2293000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>62837000</v>
+      </c>
+      <c r="E46" s="3">
         <v>57210000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>59697000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>59887000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>56801000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>55398000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>51741000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>53341000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>52252000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>47970000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>47640000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>47531000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>45539000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>44292000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>44657000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>46448000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>45383000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>46231000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>46498000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>45580000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>43350000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>45382000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>42368000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>42345000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>38682000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>42222000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>39390000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>37353000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>38428000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>38465000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>38319000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>38544000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>38214000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>37136000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>40195000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>39794000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>37697000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>36948000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>39268000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>41338000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>243000</v>
+      </c>
+      <c r="E47" s="3">
         <v>227000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>192000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>119000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>111000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>103000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>186000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>175000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>189000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>240000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>213000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>222000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>237000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>238000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>253000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>252000</v>
       </c>
-      <c r="S47" s="3" t="s">
+      <c r="T47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>346000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>358000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>357000</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>8</v>
@@ -5028,297 +5133,306 @@
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AB47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
         <v>2143000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2167000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3617000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3513000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3566000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3609000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>3672000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>3728000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>3704000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>3795000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>3855000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>4063000</v>
-      </c>
-      <c r="AO47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AP47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4625000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4726000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4690000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4618000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4742000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4284000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4155000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3856000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4092000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4045000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3880000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3851000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3865000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3812000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3793000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3619000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3681000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3640000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3645000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3990000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4620000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4681000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4473000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4366000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4249000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4251000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4421000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4495000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4497000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2548000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2503000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2488000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2483000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2464000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2401000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2348000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2349000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2292000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2411000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2300000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15291000</v>
+      </c>
+      <c r="E49" s="3">
         <v>16159000</v>
-      </c>
-      <c r="E49" s="3">
-        <v>15503000</v>
       </c>
       <c r="F49" s="3">
         <v>15503000</v>
       </c>
       <c r="G49" s="3">
+        <v>15503000</v>
+      </c>
+      <c r="H49" s="3">
         <v>15637000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12167000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11513000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11660000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12163000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12737000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12070000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12076000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12192000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12577000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>12207000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>11111000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11344000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>11510000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>11592000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>11858000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>12317000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>12371000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>12491000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>12444000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>12509000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>12516000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>12820000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>12897000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>13041000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>13047000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>14439000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>14755000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>14843000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>15026000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>15922000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>15938000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>15988000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>14251000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>14195000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>12754000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5334000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4001000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4108000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4033000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4020000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3188000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3486000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3397000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2974000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2451000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2709000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2411000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2263000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1401000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1780000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1651000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1887000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1571000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1615000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1816000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2607000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2581000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2513000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2403000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2226000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2258000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2099000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2082000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2097000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2099000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2184000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2025000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2070000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2027000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1991000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1971000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1927000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>3415000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>2000000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1923000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>88330000</v>
+      </c>
+      <c r="E54" s="3">
         <v>82323000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>84190000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>84160000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>81311000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>75140000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>71081000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>72429000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>71670000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>67443000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>66512000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>66091000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>64096000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>62320000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>62690000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>63081000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>62295000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>63298000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>63708000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>63601000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>62894000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>65015000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>61845000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>61558000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>57666000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>61247000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>60873000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>58994000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>61680000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>59672000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>61011000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>61421000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>61282000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>60381000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>64213000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>63846000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>61816000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>60969000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>57874000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>58315000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>63731000</v>
+      </c>
+      <c r="E57" s="3">
         <v>59973000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>60683000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>60938000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>57861000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>55330000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>49689000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>53317000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>51704000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>47097000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>46699000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>46795000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>43982000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>42490000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>42238000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>41003000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>39708000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>38086000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>37183000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>38922000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>38389000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>38975000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>36509000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>36255000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>33209000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>37195000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>32744000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>32560000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>34021000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>33853000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>32091000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>33227000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>32063000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>32177000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>33009000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>33580000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>32015000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>31022000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>30811000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>31037000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1668000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1714000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1418000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2025000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1546000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1449000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3846000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>311000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>350000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>346000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>562000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>345000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>352000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1267000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1021000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>800000</v>
-      </c>
-      <c r="S58" s="3">
-        <v>799000</v>
       </c>
       <c r="T58" s="3">
         <v>799000</v>
       </c>
       <c r="U58" s="3">
+        <v>799000</v>
+      </c>
+      <c r="V58" s="3">
         <v>810000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>39000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>752000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>742000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>929000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1760000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1053000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1052000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3116000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>851000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>310000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>330000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2168000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2520000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3160000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1129000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1280000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>831000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>528000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1240000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>3154000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>2166000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>653000</v>
+      </c>
+      <c r="E59" s="3">
         <v>631000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>624000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>669000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>853000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>879000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>912000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1347000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>817000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>703000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>624000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>563000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>634000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>724000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4747000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6554000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6694000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9581000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9459000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7114000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4694000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4386000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4492000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4709000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4338000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4377000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4195000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3734000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3621000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3443000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3165000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3116000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3125000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3379000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3363000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3354000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3256000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3350000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>4209000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>3848000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>70356000</v>
+      </c>
+      <c r="E60" s="3">
         <v>67017000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>68131000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>68031000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>64331000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>61604000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>58562000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>58771000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>56434000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>52357000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>51661000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>51147000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>48422000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>47957000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>48006000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>48357000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>47201000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>48466000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>47452000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>46075000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>43835000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>44103000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>41930000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>42724000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>38600000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>42624000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>40055000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>37145000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>37952000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>37626000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>37424000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>38863000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>38348000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>36685000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>37652000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>37765000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>35799000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>35612000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>38174000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>37051000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10128000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7072000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7317000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7930000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8650000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5983000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5944000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6944000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7086000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7080000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7078000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7023000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7124000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6045000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5452000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4813000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4976000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5080000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5518000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5946000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6424000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6406000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6467000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5848000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6395000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6335000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6734000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7342000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7382000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7265000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>7616000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6568000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6592000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6751000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7514000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>7490000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>7424000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>7305000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5969000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5941000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7784000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7738000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7733000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7691000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8206000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8218000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8187000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8308000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8603000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8688000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8477000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8273000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8651000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8421000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>11321000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11160000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11590000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11544000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11525000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11667000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>12673000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>13060000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>12433000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>5631000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5604000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5577000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6302000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6431000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6879000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5101000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5178000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5041000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5273000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>5429000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>5640000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>5806000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>5690000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>5452000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>4568000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>4359000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>89631000</v>
+      </c>
+      <c r="E66" s="3">
         <v>83157000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>84289000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>84738000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>82174000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>76834000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>73785000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>75071000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>73051000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>69042000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>68194000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67555000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>65336000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>63810000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>65145000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>64848000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>64299000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>65570000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>64982000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>64172000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>63423000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>65036000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>62322000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>55668000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>52220000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>56155000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>54699000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>52512000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>53806000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>51578000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>51826000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>52095000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>51875000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>50577000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>52479000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>52703000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>50513000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>49874000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>50182000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>48866000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>22808000</v>
+      </c>
+      <c r="E72" s="3">
         <v>22291000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20710000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>19622000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18616000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>17921000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16752000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15959000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15810000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14978000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14268000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13761000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>13182000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12295000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11582000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>10579000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9732000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9030000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8734000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8812000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8618000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8202000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7595000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13890000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13384000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13022000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12075000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>11965000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>12770000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12409000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13276000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13354000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>12932000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>12986000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>14202000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>13370000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>13442000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>13189000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>9663000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>9088000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-4240000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2172000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1298000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1739000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1967000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-2074000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-3084000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-3017000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1755000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1971000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-2053000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-1828000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-1602000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-1857000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-2455000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-1767000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-2004000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-2272000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-1274000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-571000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-529000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-477000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5890000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5446000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5092000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6174000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6482000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7874000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8094000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>9185000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>9326000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>9407000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>9804000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>11734000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>11143000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>11303000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>11095000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>7692000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>9449000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>614000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1682000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1186000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1110000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>784000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1260000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>879000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>241000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>915000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>791000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>589000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>664000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>958000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>787000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1079000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>926000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>768000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>368000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>267000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>486000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>666000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6226000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>577000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>444000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1021000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>186000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-730000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>423000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-796000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>469000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>499000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-138000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-1146000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>903000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>309000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>3588000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>633000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>307000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E83" s="3">
         <v>46000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>58000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>61000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>63000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>58000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>62000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>65000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>64000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>60000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>61000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>63000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>61000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>46000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>148000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>151000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>148000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>162000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>185000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>195000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>218000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>221000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>227000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>222000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>217000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>231000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>228000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>234000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>229000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>235000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>239000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>240000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>235000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>254000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>234000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>236000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>227000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>247000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>204000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>217000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-220000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3421000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1232000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2420000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-918000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7748000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2383000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2100000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1380000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4147000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>254000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>965000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1052000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3325000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1668000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1107000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-471000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2562000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1162000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1792000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1622000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3370000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1213000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1021000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1062000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4654000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-121000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-108000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-51000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3895000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-177000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1379000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-1061000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3022000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-16000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>598000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>741000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1435000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>381000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1069000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-112000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-111000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-108000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-106000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-111000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-169000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-126000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-136000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-106000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-188000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-90000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-75000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-78000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-125000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-154000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-122000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-155000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-101000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-120000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-159000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-158000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-119000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-102000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-72000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-120000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-116000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-39000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-87000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-117000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-131000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-77000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-101000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-136000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-105000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-89000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-75000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-193000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-129000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-126000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-214000</v>
+      </c>
+      <c r="E94" s="3">
         <v>425000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-269000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-24000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3564000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-224000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-136000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-286000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-87000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-577000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-180000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-166000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-149000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-244000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-414000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>77000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>39000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>183000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-115000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-58000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-99000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-205000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>68000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-148000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-130000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-170000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-124000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-129000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-230000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-168000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-108000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-875000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1039000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-87000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-267000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-129000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-177000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2273000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-192000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>101000</v>
+        <v>102000</v>
       </c>
       <c r="E96" s="3">
         <v>101000</v>
       </c>
       <c r="F96" s="3">
+        <v>101000</v>
+      </c>
+      <c r="G96" s="3">
         <v>89000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>90000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>91000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>92000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>80000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>82000</v>
       </c>
       <c r="L96" s="3">
         <v>82000</v>
       </c>
       <c r="M96" s="3">
+        <v>82000</v>
+      </c>
+      <c r="N96" s="3">
         <v>83000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>75000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>74000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>76000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-77000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-68000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-71000</v>
       </c>
       <c r="T96" s="3">
         <v>-71000</v>
       </c>
       <c r="U96" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-72000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-65000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-69000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-67000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-69000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-66000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-74000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-72000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-74000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-73000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-75000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-76000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-77000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-68000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-71000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-70000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-71000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-59000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-62000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-61000</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>-63000</v>
       </c>
       <c r="AP96" s="3">
         <v>-63000</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-63000</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1632000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2820000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2026000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-961000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1176000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2855000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1298000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1599000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-809000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-968000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-622000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-909000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-843000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1190000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1425000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-572000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1181000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1989000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-438000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1743000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2151000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-517000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-775000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-462000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>61000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2480000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>949000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-331000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-872000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2544000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>119000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1343000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1541000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1937000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>125000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-141000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1131000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-924000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1031000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E101" s="3">
         <v>5000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-22000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5000</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>7000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>10000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>6000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>18000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>20000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-9000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>6000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>18000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>20000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>17000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>7000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>11000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>16000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-46000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>5000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>4000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>18000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>11000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-43000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-78000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>7000</v>
-      </c>
-      <c r="AK101" s="3">
-        <v>34000</v>
       </c>
       <c r="AL101" s="3">
         <v>34000</v>
       </c>
       <c r="AM101" s="3">
+        <v>34000</v>
+      </c>
+      <c r="AN101" s="3">
         <v>75000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>15000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-107000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-40000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1188000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1015000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1056000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1426000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3273000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4674000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1243000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>221000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2281000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2602000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-541000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-113000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2042000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1901000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-180000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>618000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1595000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>776000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>626000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3861000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2664000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>492000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>376000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1159000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1958000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>709000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-591000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1034000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1132000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-269000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-81000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-473000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>53000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>56000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>224000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-444000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>349000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-3030000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>805000</v>
       </c>
     </row>
